--- a/steps_output/test2.xlsx
+++ b/steps_output/test2.xlsx
@@ -79,7 +79,7 @@
     <t>TimeToFeeding</t>
   </si>
   <si>
-    <t>days_since_first</t>
+    <t>days</t>
   </si>
   <si>
     <t>Bernie</t>
